--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.4602599926606</v>
+        <v>4.624792248807347</v>
       </c>
       <c r="D2" t="n">
-        <v>59.86398096596793</v>
+        <v>9.727896906969789</v>
       </c>
       <c r="E2" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F2" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.58210196046037</v>
+        <v>7.732091568574811</v>
       </c>
       <c r="D3" t="n">
-        <v>47.5109540746984</v>
+        <v>7.72053003713849</v>
       </c>
       <c r="E3" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F3" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.062230026332877</v>
+        <v>0.8226123792790925</v>
       </c>
       <c r="D4" t="n">
-        <v>58.46622013968434</v>
+        <v>9.500760772698705</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F4" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.4487400689385</v>
+        <v>6.247920261202506</v>
       </c>
       <c r="D5" t="n">
-        <v>38.24134345097345</v>
+        <v>6.214218310783185</v>
       </c>
       <c r="E5" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.69401960125317</v>
+        <v>2.22527818520364</v>
       </c>
       <c r="D6" t="n">
-        <v>48.4514191586213</v>
+        <v>7.873355613275962</v>
       </c>
       <c r="E6" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.18114451746392</v>
+        <v>4.416935984087886</v>
       </c>
       <c r="D7" t="n">
-        <v>27.19522039454289</v>
+        <v>4.41922331411322</v>
       </c>
       <c r="E7" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F7" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.54366891994606</v>
+        <v>3.663346199491236</v>
       </c>
       <c r="D8" t="n">
-        <v>21.83854669236272</v>
+        <v>3.548763837508943</v>
       </c>
       <c r="E8" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F8" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.70878282505807</v>
+        <v>5.965177209071937</v>
       </c>
       <c r="D9" t="n">
-        <v>36.78535481094973</v>
+        <v>5.977620156779332</v>
       </c>
       <c r="E9" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F9" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59068345176566</v>
+        <v>5.620986060911919</v>
       </c>
       <c r="D10" t="n">
-        <v>34.62141140391473</v>
+        <v>5.625979353136144</v>
       </c>
       <c r="E10" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F10" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.19261085004617</v>
+        <v>6.856299263132503</v>
       </c>
       <c r="D11" t="n">
-        <v>42.82936706272164</v>
+        <v>6.959772147692267</v>
       </c>
       <c r="E11" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F11" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.97377860534345</v>
+        <v>4.05823902336831</v>
       </c>
       <c r="D12" t="n">
-        <v>24.98770536710799</v>
+        <v>4.060502122155048</v>
       </c>
       <c r="E12" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F12" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.38305484039751</v>
+        <v>4.612246411564596</v>
       </c>
       <c r="D13" t="n">
-        <v>27.99789368154336</v>
+        <v>4.549657723250797</v>
       </c>
       <c r="E13" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F13" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.27115179125576</v>
+        <v>6.544062166079061</v>
       </c>
       <c r="D14" t="n">
-        <v>41.01600545615889</v>
+        <v>6.66510088662582</v>
       </c>
       <c r="E14" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F14" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.42254239189203</v>
+        <v>4.618663138682455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.14513558939542</v>
+        <v>4.736084533276756</v>
       </c>
       <c r="E15" t="n">
-        <v>10.96959820071033</v>
+        <v>1.782559707615428</v>
       </c>
       <c r="F15" t="n">
-        <v>11.53941523213382</v>
+        <v>1.875154975221746</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
